--- a/erp-server/erp-server-file/src/main/resources/excel/wms/awdInventoryExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/awdInventoryExport.xlsx
@@ -85,7 +85,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.totalOnhandQuantity}</t>
+    <t>{.totalOnhandQty}</t>
   </si>
   <si>
     <t>{.availableDistributableQty}</t>
